--- a/ig/StructureDefinition-procedure-aps.xlsx
+++ b/ig/StructureDefinition-procedure-aps.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T19:34:43+08:00</t>
+    <t>2026-04-25T19:59:58+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/StructureDefinition-procedure-aps.xlsx
+++ b/ig/StructureDefinition-procedure-aps.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T19:59:58+08:00</t>
+    <t>2026-04-25T20:27:14+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/StructureDefinition-procedure-aps.xlsx
+++ b/ig/StructureDefinition-procedure-aps.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-25T20:27:14+08:00</t>
+    <t>2026-04-25T20:44:16+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
